--- a/Indomie Clients Details/Gourmet/Gourmet - 23-06-26.xlsx
+++ b/Indomie Clients Details/Gourmet/Gourmet - 23-06-26.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{601669F0-BDC8-4A05-AE29-20AA7BB0E3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{658367C3-12EC-4620-B21A-368615559251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -3841,7 +3841,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -3869,7 +3869,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -5096,7 +5096,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -5124,7 +5124,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -6351,7 +6351,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -6379,7 +6379,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -7606,7 +7606,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -7634,7 +7634,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -8862,7 +8862,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -8890,7 +8890,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -10117,7 +10117,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -10145,7 +10145,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -11417,7 +11417,7 @@
       <c r="M4" s="375"/>
       <c r="N4" s="391">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="391"/>
       <c r="P4" s="391"/>
@@ -11451,7 +11451,7 @@
       <c r="M5" s="375"/>
       <c r="N5" s="391">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="376"/>
       <c r="P5" s="376"/>
@@ -12787,7 +12787,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -12815,7 +12815,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -14042,7 +14042,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -14070,7 +14070,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -15297,7 +15297,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -15325,7 +15325,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -19302,7 +19302,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -19330,7 +19330,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -20557,7 +20557,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -20585,7 +20585,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -21812,7 +21812,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -21840,7 +21840,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -23067,7 +23067,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -23095,7 +23095,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -24309,7 +24309,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -24330,7 +24330,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -25506,7 +25506,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -25527,7 +25527,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -26708,7 +26708,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -26729,7 +26729,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -27908,7 +27908,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -27929,7 +27929,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -29110,7 +29110,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -29131,7 +29131,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -30310,7 +30310,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -30330,7 +30330,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -31514,7 +31514,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -31542,7 +31542,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -31753,7 +31753,7 @@
       </c>
       <c r="U14" s="163">
         <f>+'1'!P35</f>
-        <v>29197.061974800003</v>
+        <v>25115.739688800008</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -31806,7 +31806,7 @@
       </c>
       <c r="U15" s="163">
         <f>+'2'!P35</f>
-        <v>29197.061974800003</v>
+        <v>25115.739688800008</v>
       </c>
       <c r="XFD15" t="s">
         <v>81</v>
@@ -31987,11 +31987,11 @@
       <c r="G18" s="113"/>
       <c r="H18" s="171">
         <f>+'1'!H18+'2'!H18+'4'!H18+'3'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18+'13'!H18+'14'!H18+'15'!H18+'16'!H18+'17'!H18+'18'!H18+'19'!H18+'20'!H18+'21'!H18+'22'!H18+'23'!H18+'24'!H18+'25'!H18+'26'!H18+'27'!H18+'28'!H18</f>
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>8394</v>
+        <v>0</v>
       </c>
       <c r="J18" s="171">
         <f>+'1'!J18+'2'!J18+'4'!J18+'3'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18</f>
@@ -32003,23 +32003,23 @@
       </c>
       <c r="L18" s="174">
         <f>+'1'!L18+'2'!L18+'4'!L18+'3'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18</f>
-        <v>1510.9199999999998</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="2"/>
-        <v>6883.08</v>
+        <v>0</v>
       </c>
       <c r="N18" s="100">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>1238.9543999999999</v>
+        <v>0</v>
       </c>
       <c r="O18" s="100">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>40.610171999999999</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="0"/>
-        <v>8162.6445719999992</v>
+        <v>0</v>
       </c>
       <c r="T18" s="162" t="str">
         <f>+'5'!A5</f>
@@ -32457,7 +32457,7 @@
       <c r="B25" s="321"/>
       <c r="C25" s="322">
         <f>H25/40</f>
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D25" s="316"/>
       <c r="E25" s="316"/>
@@ -32468,11 +32468,11 @@
       </c>
       <c r="H25" s="176">
         <f t="shared" si="3"/>
-        <v>960</v>
+        <v>800</v>
       </c>
       <c r="I25" s="177">
         <f t="shared" si="3"/>
-        <v>60049.200000000004</v>
+        <v>51655.200000000004</v>
       </c>
       <c r="J25" s="176">
         <f t="shared" si="3"/>
@@ -32484,23 +32484,23 @@
       </c>
       <c r="L25" s="178">
         <f t="shared" si="3"/>
-        <v>10808.855999999998</v>
+        <v>9297.9359999999979</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="3"/>
-        <v>49240.344000000005</v>
+        <v>42357.264000000003</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>8863.261919999999</v>
+        <v>7624.3075199999994</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>290.51802959999998</v>
+        <v>249.9078576</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>58394.123949599991</v>
+        <v>50231.479377600001</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -32960,7 +32960,7 @@
       </c>
       <c r="U42" s="164">
         <f>SUM(U14:U40)</f>
-        <v>58394.123949600005</v>
+        <v>50231.479377600015</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -32993,7 +32993,7 @@
       <c r="O44" s="333"/>
       <c r="P44" s="151">
         <f>I25</f>
-        <v>60049.200000000004</v>
+        <v>51655.200000000004</v>
       </c>
     </row>
     <row r="45" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33014,7 +33014,7 @@
       <c r="O45" s="335"/>
       <c r="P45" s="152">
         <f>L25</f>
-        <v>10808.855999999998</v>
+        <v>9297.9359999999979</v>
       </c>
     </row>
     <row r="46" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33057,7 +33057,7 @@
       <c r="O47" s="335"/>
       <c r="P47" s="152">
         <f>P44-P45-P46</f>
-        <v>49240.344000000005</v>
+        <v>42357.26400000001</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33082,7 +33082,7 @@
       </c>
       <c r="P48" s="152">
         <f>N25</f>
-        <v>8863.261919999999</v>
+        <v>7624.3075199999994</v>
       </c>
     </row>
     <row r="49" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33104,7 +33104,7 @@
       <c r="O49" s="337"/>
       <c r="P49" s="152">
         <f>P47+P48</f>
-        <v>58103.605920000002</v>
+        <v>49981.571520000012</v>
       </c>
     </row>
     <row r="50" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -33129,7 +33129,7 @@
       </c>
       <c r="P50" s="152">
         <f>O50*P49</f>
-        <v>1452.5901480000002</v>
+        <v>1249.5392880000004</v>
       </c>
     </row>
     <row r="51" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -33139,7 +33139,7 @@
       <c r="O51" s="315"/>
       <c r="P51" s="159">
         <f>P49+P50</f>
-        <v>59556.196068000005</v>
+        <v>51231.110808000012</v>
       </c>
     </row>
     <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -33297,7 +33297,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -33317,7 +33317,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -34575,7 +34575,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -34603,7 +34603,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -35027,11 +35027,11 @@
       </c>
       <c r="G18" s="113"/>
       <c r="H18" s="114">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I18" s="115">
         <f t="shared" si="3"/>
-        <v>4197</v>
+        <v>0</v>
       </c>
       <c r="J18" s="116"/>
       <c r="K18" s="1">
@@ -35040,23 +35040,23 @@
       </c>
       <c r="L18" s="104">
         <f t="shared" si="5"/>
-        <v>755.45999999999992</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="6"/>
-        <v>3441.54</v>
+        <v>0</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>619.47719999999993</v>
+        <v>0</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="1"/>
-        <v>20.305085999999999</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="2"/>
-        <v>4081.3222859999996</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="114">
         <v>0</v>
@@ -35433,11 +35433,11 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>30024.600000000002</v>
+        <v>25827.600000000002</v>
       </c>
       <c r="J25" s="137"/>
       <c r="K25" s="138">
@@ -35446,23 +35446,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>5404.427999999999</v>
+        <v>4648.9679999999989</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>24620.172000000002</v>
+        <v>21178.632000000001</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>4431.6309599999995</v>
+        <v>3812.1537599999997</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>145.25901479999999</v>
+        <v>124.9539288</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>29197.061974799995</v>
+        <v>25115.7396888</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -35512,7 +35512,7 @@
       <c r="O28" s="333"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>30024.600000000002</v>
+        <v>25827.600000000002</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35533,7 +35533,7 @@
       <c r="O29" s="335"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>5404.427999999999</v>
+        <v>4648.9679999999989</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35576,7 +35576,7 @@
       <c r="O31" s="335"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>24620.172000000002</v>
+        <v>21178.632000000005</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35601,7 +35601,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>4431.6309599999995</v>
+        <v>3812.1537599999997</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35623,7 +35623,7 @@
       <c r="O33" s="337"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>29051.802960000001</v>
+        <v>24990.785760000006</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -35648,7 +35648,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>145.25901480000002</v>
+        <v>124.95392880000003</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -35658,7 +35658,7 @@
       <c r="O35" s="315"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>29197.061974800003</v>
+        <v>25115.739688800008</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -35830,7 +35830,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -35858,7 +35858,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -36282,11 +36282,11 @@
       </c>
       <c r="G18" s="113"/>
       <c r="H18" s="114">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I18" s="115">
         <f t="shared" si="2"/>
-        <v>4197</v>
+        <v>0</v>
       </c>
       <c r="J18" s="116"/>
       <c r="K18" s="1">
@@ -36295,23 +36295,23 @@
       </c>
       <c r="L18" s="104">
         <f t="shared" si="4"/>
-        <v>755.45999999999992</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="5"/>
-        <v>3441.54</v>
+        <v>0</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>619.47719999999993</v>
+        <v>0</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="6"/>
-        <v>20.305085999999999</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="1"/>
-        <v>4081.3222859999996</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="114">
         <v>0</v>
@@ -36689,11 +36689,11 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>30024.600000000002</v>
+        <v>25827.600000000002</v>
       </c>
       <c r="J25" s="137"/>
       <c r="K25" s="138">
@@ -36702,23 +36702,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>5404.427999999999</v>
+        <v>4648.9679999999989</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>24620.172000000002</v>
+        <v>21178.632000000001</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>4431.6309599999995</v>
+        <v>3812.1537599999997</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>145.25901479999999</v>
+        <v>124.9539288</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>29197.061974799995</v>
+        <v>25115.7396888</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -36768,7 +36768,7 @@
       <c r="O28" s="333"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>30024.600000000002</v>
+        <v>25827.600000000002</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -36789,7 +36789,7 @@
       <c r="O29" s="335"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>5404.427999999999</v>
+        <v>4648.9679999999989</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -36832,7 +36832,7 @@
       <c r="O31" s="335"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>24620.172000000002</v>
+        <v>21178.632000000005</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -36857,7 +36857,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>4431.6309599999995</v>
+        <v>3812.1537599999997</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -36879,7 +36879,7 @@
       <c r="O33" s="337"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>29051.802960000001</v>
+        <v>24990.785760000006</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -36904,7 +36904,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>145.25901480000002</v>
+        <v>124.95392880000003</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -36914,7 +36914,7 @@
       <c r="O35" s="315"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>29197.061974800003</v>
+        <v>25115.739688800008</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -37086,7 +37086,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -37114,7 +37114,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -38340,7 +38340,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -38368,7 +38368,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -39595,7 +39595,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -39623,7 +39623,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -40851,7 +40851,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -40879,7 +40879,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
